--- a/data/廠商代碼.xlsx
+++ b/data/廠商代碼.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1233"/>
+  <dimension ref="A1:B1234"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15224,6 +15224,18 @@
         </is>
       </c>
     </row>
+    <row r="1234">
+      <c r="A1234" t="inlineStr">
+        <is>
+          <t>C91</t>
+        </is>
+      </c>
+      <c r="B1234" t="inlineStr">
+        <is>
+          <t>晴子</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/廠商代碼.xlsx
+++ b/data/廠商代碼.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1234"/>
+  <dimension ref="A1:B1235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15236,6 +15236,18 @@
         </is>
       </c>
     </row>
+    <row r="1235">
+      <c r="A1235" t="inlineStr">
+        <is>
+          <t>B68</t>
+        </is>
+      </c>
+      <c r="B1235" t="inlineStr">
+        <is>
+          <t>谷奈兒</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
